--- a/Data/Tables/__tables__.xlsx
+++ b/Data/Tables/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -120,6 +120,24 @@
   </si>
   <si>
     <t>c</t>
+  </si>
+  <si>
+    <t>Base.UITemplateTable</t>
+  </si>
+  <si>
+    <t>UITemplate</t>
+  </si>
+  <si>
+    <t>UITemplate_UI模板表.xlsx</t>
+  </si>
+  <si>
+    <t>Battle.AttributeTable</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Attribute_属性表.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1061,14 +1079,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="4" width="32.375" customWidth="1"/>
     <col min="5" max="5" width="24.375" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col min="6" max="6" width="75" customWidth="1"/>
+    <col min="7" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
@@ -1175,6 +1194,40 @@
         <v>29</v>
       </c>
       <c r="H4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
         <v>30</v>
       </c>
     </row>
